--- a/category_config.xlsx
+++ b/category_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,21 @@
       </c>
       <c r="C2" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>动作识别</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>知名IP</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/category_config.xlsx
+++ b/category_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>常识与专业领域</t>
+          <t>时序能力</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>知名IP</t>
+          <t>事件时间定位</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>动作识别</t>
+          <t>推理能力</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>知名IP</t>
+          <t>预测性推理</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>视觉基础能力</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>颜色识别</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>属性识别</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>数量统计</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>10</v>
       </c>
     </row>

--- a/category_config.xlsx
+++ b/category_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>时序能力</t>
+          <t>视觉基础能力</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>事件时间定位</t>
+          <t>物体识别</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>预测性推理</t>
+          <t>空间推理</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,31 +466,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>视觉基础能力</t>
+          <t>综合能力</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>颜色识别</t>
+          <t>情感与意图</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>属性识别</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>数量统计</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
